--- a/00 Raw data/SDG/Publications_by_SDG_-_National_Taiwan_University_of_Science_and_Technology.xlsx
+++ b/00 Raw data/SDG/Publications_by_SDG_-_National_Taiwan_University_of_Science_and_Technology.xlsx
@@ -90,7 +90,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2018 to 2025</t>
+          <t>2017 to 2025</t>
         </is>
       </c>
     </row>
@@ -157,7 +157,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>8 July 2026</t>
+          <t>5 August 2026</t>
         </is>
       </c>
     </row>
@@ -169,7 +169,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>16 July 2026</t>
+          <t>13 August 2026</t>
         </is>
       </c>
     </row>
@@ -215,7 +215,7 @@
         <v>0.63</v>
       </c>
       <c r="D13" t="n">
-        <v>114.0</v>
+        <v>115.0</v>
       </c>
     </row>
     <row r="14">
@@ -225,13 +225,13 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>35.0</v>
+        <v>36.0</v>
       </c>
       <c r="C14" t="n">
         <v>0.93</v>
       </c>
       <c r="D14" t="n">
-        <v>453.0</v>
+        <v>520.0</v>
       </c>
     </row>
     <row r="15">
@@ -241,13 +241,13 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>707.0</v>
+        <v>758.0</v>
       </c>
       <c r="C15" t="n">
         <v>1.24</v>
       </c>
       <c r="D15" t="n">
-        <v>14969.0</v>
+        <v>17377.0</v>
       </c>
     </row>
     <row r="16">
@@ -257,13 +257,13 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>508.0</v>
+        <v>543.0</v>
       </c>
       <c r="C16" t="n">
-        <v>2.79</v>
+        <v>2.77</v>
       </c>
       <c r="D16" t="n">
-        <v>16975.0</v>
+        <v>18688.0</v>
       </c>
     </row>
     <row r="17">
@@ -273,13 +273,13 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>13.0</v>
+        <v>14.0</v>
       </c>
       <c r="C17" t="n">
-        <v>1.92</v>
+        <v>1.74</v>
       </c>
       <c r="D17" t="n">
-        <v>106.0</v>
+        <v>111.0</v>
       </c>
     </row>
     <row r="18">
@@ -289,13 +289,13 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>348.0</v>
+        <v>363.0</v>
       </c>
       <c r="C18" t="n">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="D18" t="n">
-        <v>11176.0</v>
+        <v>12290.0</v>
       </c>
     </row>
     <row r="19">
@@ -305,13 +305,13 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1813.0</v>
+        <v>1973.0</v>
       </c>
       <c r="C19" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="D19" t="n">
-        <v>45058.0</v>
+        <v>51617.0</v>
       </c>
     </row>
     <row r="20">
@@ -321,13 +321,13 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>177.0</v>
+        <v>182.0</v>
       </c>
       <c r="C20" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="D20" t="n">
-        <v>3277.0</v>
+        <v>3489.0</v>
       </c>
     </row>
     <row r="21">
@@ -337,13 +337,13 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1025.0</v>
+        <v>1101.0</v>
       </c>
       <c r="C21" t="n">
-        <v>1.24</v>
+        <v>1.21</v>
       </c>
       <c r="D21" t="n">
-        <v>18761.0</v>
+        <v>20521.0</v>
       </c>
     </row>
     <row r="22">
@@ -353,13 +353,13 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>36.0</v>
+        <v>38.0</v>
       </c>
       <c r="C22" t="n">
         <v>0.62</v>
       </c>
       <c r="D22" t="n">
-        <v>282.0</v>
+        <v>338.0</v>
       </c>
     </row>
     <row r="23">
@@ -369,13 +369,13 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>342.0</v>
+        <v>366.0</v>
       </c>
       <c r="C23" t="n">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="D23" t="n">
-        <v>4986.0</v>
+        <v>5764.0</v>
       </c>
     </row>
     <row r="24">
@@ -385,13 +385,13 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>280.0</v>
+        <v>296.0</v>
       </c>
       <c r="C24" t="n">
-        <v>1.49</v>
+        <v>1.45</v>
       </c>
       <c r="D24" t="n">
-        <v>6989.0</v>
+        <v>7607.0</v>
       </c>
     </row>
     <row r="25">
@@ -401,13 +401,13 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>332.0</v>
+        <v>341.0</v>
       </c>
       <c r="C25" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="D25" t="n">
-        <v>8518.0</v>
+        <v>8919.0</v>
       </c>
     </row>
     <row r="26">
@@ -417,13 +417,13 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>52.0</v>
+        <v>53.0</v>
       </c>
       <c r="C26" t="n">
-        <v>2.37</v>
+        <v>2.33</v>
       </c>
       <c r="D26" t="n">
-        <v>2160.0</v>
+        <v>2192.0</v>
       </c>
     </row>
     <row r="27">
@@ -433,13 +433,13 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>50.0</v>
+        <v>52.0</v>
       </c>
       <c r="C27" t="n">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="D27" t="n">
-        <v>1542.0</v>
+        <v>1585.0</v>
       </c>
     </row>
     <row r="28">
@@ -449,13 +449,13 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>42.0</v>
+        <v>45.0</v>
       </c>
       <c r="C28" t="n">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="D28" t="n">
-        <v>520.0</v>
+        <v>609.0</v>
       </c>
     </row>
     <row r="29">
@@ -465,13 +465,13 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>4628.0</v>
+        <v>4988.0</v>
       </c>
       <c r="C29" t="n">
-        <v>1.48</v>
+        <v>1.46</v>
       </c>
       <c r="D29" t="n">
-        <v>109559.0</v>
+        <v>123502.0</v>
       </c>
     </row>
     <row r="30">
